--- a/aroma2.xlsx
+++ b/aroma2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB4C81F1-85C2-614F-8238-D3BCEBFC2336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE34CCDE-91E3-2149-AB11-4CAC2958B13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="212">
-  <si>
-    <t xml:space="preserve">marca </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="214">
   <si>
     <t>stock</t>
   </si>
@@ -658,16 +655,33 @@
   </si>
   <si>
     <t>precio_gran_mayor</t>
+  </si>
+  <si>
+    <t>marca</t>
+  </si>
+  <si>
+    <t>imagen</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1541643600914-78b084683601?w=500&amp;q=80</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -690,13 +704,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -713,25 +730,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D0EE2CF-71C5-D741-83C1-EA5EDA49B420}" name="Tabla1" displayName="Tabla1" ref="A1:F163" totalsRowShown="0">
-  <autoFilter ref="A1:F163" xr:uid="{1D0EE2CF-71C5-D741-83C1-EA5EDA49B420}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D0EE2CF-71C5-D741-83C1-EA5EDA49B420}" name="Tabla1" displayName="Tabla1" ref="A1:H163" totalsRowShown="0">
+  <autoFilter ref="A1:H163" xr:uid="{1D0EE2CF-71C5-D741-83C1-EA5EDA49B420}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{F8C914C5-7B37-4849-9B27-FE7D2B9C89D4}" name="Nombre"/>
-    <tableColumn id="2" xr3:uid="{8648274B-B788-3C44-A5E0-94F22772E93A}" name="marca "/>
+    <tableColumn id="2" xr3:uid="{8648274B-B788-3C44-A5E0-94F22772E93A}" name="marca"/>
     <tableColumn id="3" xr3:uid="{F6E3D45D-BE40-7E44-8E14-617333F054D3}" name="stock"/>
     <tableColumn id="4" xr3:uid="{4FB50FE2-3E4E-9B46-9925-755B1E4CF7EE}" name="precio de compra"/>
     <tableColumn id="5" xr3:uid="{DFF41EA6-0C03-3C40-B043-B25C58902F14}" name="precio_venta"/>
     <tableColumn id="6" xr3:uid="{7E44F4E0-0431-6F47-98B9-E8CF3406F787}" name="precio_mayor"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9729EF13-AACD-C34F-B217-8F888CA8BBD3}" name="Tabla2" displayName="Tabla2" ref="G1:G2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="G1:G2" xr:uid="{9729EF13-AACD-C34F-B217-8F888CA8BBD3}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{566712F9-069B-E747-9435-CB4237BFD675}" name="precio_gran_mayor"/>
+    <tableColumn id="7" xr3:uid="{1924C80F-F0E6-224F-B1CA-1051DC596397}" name="precio_gran_mayor"/>
+    <tableColumn id="8" xr3:uid="{41EDF2A5-BE6F-5A4E-8600-0DD9A4BB5506}" name="imagen"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1054,41 +1063,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB0897F-7FA2-0741-BEB5-E9CDF8F18928}">
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="7" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.5078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>206</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1099,13 +1112,22 @@
       <c r="E2">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>17.5</v>
+      </c>
+      <c r="G2">
+        <v>15.5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1116,13 +1138,19 @@
       <c r="E3">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1133,13 +1161,19 @@
       <c r="E4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1150,13 +1184,19 @@
       <c r="E5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1167,13 +1207,19 @@
       <c r="E6">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1184,13 +1230,19 @@
       <c r="E7">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1201,13 +1253,19 @@
       <c r="E8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1218,13 +1276,19 @@
       <c r="E9">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1235,13 +1299,19 @@
       <c r="E10">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1252,30 +1322,42 @@
       <c r="E11">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>9.99</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="F12">
+        <v>13.5</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>9.99</v>
-      </c>
-      <c r="E12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1286,13 +1368,19 @@
       <c r="E13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1303,13 +1391,19 @@
       <c r="E14">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1320,30 +1414,42 @@
       <c r="E15">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>13.5</v>
+      </c>
+      <c r="G15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>9.99</v>
+      </c>
+      <c r="E16">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>13.5</v>
+      </c>
+      <c r="G16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>9.99</v>
-      </c>
-      <c r="E16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1354,13 +1460,19 @@
       <c r="E17">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1371,13 +1483,19 @@
       <c r="E18">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>16</v>
+      </c>
+      <c r="G18">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1388,13 +1506,19 @@
       <c r="E19">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <v>27</v>
+      </c>
+      <c r="G19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1405,13 +1529,19 @@
       <c r="E20">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <v>27</v>
+      </c>
+      <c r="G20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1422,13 +1552,19 @@
       <c r="E21">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1439,13 +1575,19 @@
       <c r="E22">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <v>24</v>
+      </c>
+      <c r="G22">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1456,13 +1598,19 @@
       <c r="E23">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <v>24</v>
+      </c>
+      <c r="G23">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1473,13 +1621,19 @@
       <c r="E24">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <v>16</v>
+      </c>
+      <c r="G24">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1490,13 +1644,19 @@
       <c r="E25">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <v>16</v>
+      </c>
+      <c r="G25">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1507,13 +1667,19 @@
       <c r="E26">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>16</v>
+      </c>
+      <c r="G26">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1524,13 +1690,19 @@
       <c r="E27">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <v>19</v>
+      </c>
+      <c r="G27">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1541,13 +1713,19 @@
       <c r="E28">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1558,13 +1736,19 @@
       <c r="E29">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F29">
+        <v>19</v>
+      </c>
+      <c r="G29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1575,13 +1759,19 @@
       <c r="E30">
         <v>25</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F30">
+        <v>19</v>
+      </c>
+      <c r="G30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1592,13 +1782,19 @@
       <c r="E31">
         <v>20</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31">
+        <v>17.5</v>
+      </c>
+      <c r="G31">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1609,13 +1805,19 @@
       <c r="E32">
         <v>25</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32">
+        <v>24</v>
+      </c>
+      <c r="G32">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1626,13 +1828,19 @@
       <c r="E33">
         <v>20</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33">
+        <v>17.5</v>
+      </c>
+      <c r="G33">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1643,13 +1851,19 @@
       <c r="E34">
         <v>20</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F34">
+        <v>17.5</v>
+      </c>
+      <c r="G34">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1660,13 +1874,19 @@
       <c r="E35">
         <v>20</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <v>17.5</v>
+      </c>
+      <c r="G35">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1677,13 +1897,19 @@
       <c r="E36">
         <v>20</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>17.5</v>
+      </c>
+      <c r="G36">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1694,13 +1920,19 @@
       <c r="E37">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <v>27</v>
+      </c>
+      <c r="G37">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1711,13 +1943,19 @@
       <c r="E38">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <v>27</v>
+      </c>
+      <c r="G38">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1728,13 +1966,19 @@
       <c r="E39">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F39">
+        <v>27</v>
+      </c>
+      <c r="G39">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1745,13 +1989,19 @@
       <c r="E40">
         <v>28</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F40">
+        <v>27</v>
+      </c>
+      <c r="G40">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
         <v>47</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1762,13 +2012,19 @@
       <c r="E41">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>24</v>
+      </c>
+      <c r="G41">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1779,13 +2035,19 @@
       <c r="E42">
         <v>20</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>17.5</v>
+      </c>
+      <c r="G42">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1796,13 +2058,19 @@
       <c r="E43">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>20</v>
+      </c>
+      <c r="G43">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1813,13 +2081,19 @@
       <c r="E44">
         <v>25</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F44">
+        <v>24</v>
+      </c>
+      <c r="G44">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1830,13 +2104,19 @@
       <c r="E45">
         <v>25</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <v>24</v>
+      </c>
+      <c r="G45">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1847,13 +2127,19 @@
       <c r="E46">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46">
+        <v>24</v>
+      </c>
+      <c r="G46">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1864,13 +2150,19 @@
       <c r="E47">
         <v>25</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47">
+        <v>24</v>
+      </c>
+      <c r="G47">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1881,251 +2173,341 @@
       <c r="E48">
         <v>22</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48">
+        <v>20</v>
+      </c>
+      <c r="G48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
         <v>56</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>9.99</v>
+      </c>
+      <c r="E49">
+        <v>15</v>
+      </c>
+      <c r="F49">
+        <v>13.5</v>
+      </c>
+      <c r="G49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>57</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>9.99</v>
-      </c>
-      <c r="E49">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>9.99</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="F50">
+        <v>13.5</v>
+      </c>
+      <c r="G50">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>58</v>
       </c>
-      <c r="B50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>9.99</v>
-      </c>
-      <c r="E50">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>59</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>9.99</v>
+      </c>
+      <c r="E51">
+        <v>15</v>
+      </c>
+      <c r="F51">
+        <v>13.5</v>
+      </c>
+      <c r="G51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>60</v>
       </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>9.99</v>
-      </c>
-      <c r="E51">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>9.99</v>
+      </c>
+      <c r="E52">
+        <v>15</v>
+      </c>
+      <c r="F52">
+        <v>13.5</v>
+      </c>
+      <c r="G52">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>61</v>
       </c>
-      <c r="B52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>9.99</v>
-      </c>
-      <c r="E52">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>9.99</v>
+      </c>
+      <c r="E53">
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <v>13.5</v>
+      </c>
+      <c r="G53">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>62</v>
       </c>
-      <c r="B53" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>9.99</v>
-      </c>
-      <c r="E53">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>9.99</v>
+      </c>
+      <c r="E54">
+        <v>15</v>
+      </c>
+      <c r="F54">
+        <v>13.5</v>
+      </c>
+      <c r="G54">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>63</v>
       </c>
-      <c r="B54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>9.99</v>
-      </c>
-      <c r="E54">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>9.99</v>
+      </c>
+      <c r="E55">
+        <v>15</v>
+      </c>
+      <c r="F55">
+        <v>13.5</v>
+      </c>
+      <c r="G55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>64</v>
       </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>9.99</v>
-      </c>
-      <c r="E55">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>65</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>9.99</v>
+      </c>
+      <c r="E56">
+        <v>15</v>
+      </c>
+      <c r="F56">
+        <v>13.5</v>
+      </c>
+      <c r="G56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>66</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
-        <v>9.99</v>
-      </c>
-      <c r="E56">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>9.99</v>
+      </c>
+      <c r="E57">
+        <v>15</v>
+      </c>
+      <c r="F57">
+        <v>13.5</v>
+      </c>
+      <c r="G57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>67</v>
       </c>
-      <c r="B57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>9.99</v>
-      </c>
-      <c r="E57">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>9.99</v>
+      </c>
+      <c r="E58">
+        <v>15</v>
+      </c>
+      <c r="F58">
+        <v>13.5</v>
+      </c>
+      <c r="G58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>68</v>
       </c>
-      <c r="B58" t="s">
-        <v>66</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>9.99</v>
-      </c>
-      <c r="E58">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>9.99</v>
+      </c>
+      <c r="E59">
+        <v>15</v>
+      </c>
+      <c r="F59">
+        <v>13.5</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="B59" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>9.99</v>
-      </c>
-      <c r="E59">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>9.99</v>
+      </c>
+      <c r="E60">
+        <v>15</v>
+      </c>
+      <c r="F60">
+        <v>13.5</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>70</v>
       </c>
-      <c r="B60" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>9.99</v>
-      </c>
-      <c r="E60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>71</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>9.99</v>
+      </c>
+      <c r="E61">
+        <v>15</v>
+      </c>
+      <c r="F61">
+        <v>13.5</v>
+      </c>
+      <c r="G61">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>72</v>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>9.99</v>
-      </c>
-      <c r="E61">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>9.99</v>
+      </c>
+      <c r="E62">
+        <v>15</v>
+      </c>
+      <c r="F62">
+        <v>13.5</v>
+      </c>
+      <c r="G62">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
         <v>73</v>
       </c>
-      <c r="B62" t="s">
-        <v>72</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>9.99</v>
-      </c>
-      <c r="E62">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>74</v>
-      </c>
-      <c r="B63" t="s">
-        <v>75</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2136,13 +2518,19 @@
       <c r="E63">
         <v>28</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F63">
+        <v>27</v>
+      </c>
+      <c r="G63">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -2153,13 +2541,19 @@
       <c r="E64">
         <v>28</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F64">
+        <v>27</v>
+      </c>
+      <c r="G64">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -2170,13 +2564,19 @@
       <c r="E65">
         <v>28</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F65">
+        <v>27</v>
+      </c>
+      <c r="G65">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2187,13 +2587,19 @@
       <c r="E66">
         <v>28</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F66">
+        <v>27</v>
+      </c>
+      <c r="G66">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2204,81 +2610,111 @@
       <c r="E67">
         <v>28</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F67">
+        <v>27</v>
+      </c>
+      <c r="G67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" t="s">
         <v>80</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>9.99</v>
+      </c>
+      <c r="E68">
+        <v>15</v>
+      </c>
+      <c r="F68">
+        <v>13.5</v>
+      </c>
+      <c r="G68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>81</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>9.99</v>
-      </c>
-      <c r="E68">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>82</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>9.99</v>
+      </c>
+      <c r="E69">
+        <v>15</v>
+      </c>
+      <c r="F69">
+        <v>13.5</v>
+      </c>
+      <c r="G69">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>83</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69">
-        <v>9.99</v>
-      </c>
-      <c r="E69">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>9.99</v>
+      </c>
+      <c r="E70">
+        <v>15</v>
+      </c>
+      <c r="F70">
+        <v>13.5</v>
+      </c>
+      <c r="G70">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>84</v>
       </c>
-      <c r="B70" t="s">
-        <v>83</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70">
-        <v>9.99</v>
-      </c>
-      <c r="E70">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>85</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>9.99</v>
+      </c>
+      <c r="E71">
+        <v>15</v>
+      </c>
+      <c r="F71">
+        <v>13.5</v>
+      </c>
+      <c r="G71">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
         <v>86</v>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>9.99</v>
-      </c>
-      <c r="E71">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>87</v>
-      </c>
-      <c r="B72" t="s">
-        <v>88</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -2289,13 +2725,19 @@
       <c r="E72">
         <v>22</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F72">
+        <v>20</v>
+      </c>
+      <c r="G72">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -2306,64 +2748,88 @@
       <c r="E73">
         <v>22</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F73">
+        <v>20</v>
+      </c>
+      <c r="G73">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" t="s">
         <v>90</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>9.99</v>
+      </c>
+      <c r="E74">
+        <v>15</v>
+      </c>
+      <c r="F74">
+        <v>13.5</v>
+      </c>
+      <c r="G74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>91</v>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74">
-        <v>9.99</v>
-      </c>
-      <c r="E74">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>92</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>9.99</v>
+      </c>
+      <c r="E75">
+        <v>15</v>
+      </c>
+      <c r="F75">
+        <v>13.5</v>
+      </c>
+      <c r="G75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>93</v>
       </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
-        <v>9.99</v>
-      </c>
-      <c r="E75">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>9.99</v>
+      </c>
+      <c r="E76">
+        <v>15</v>
+      </c>
+      <c r="F76">
+        <v>13.5</v>
+      </c>
+      <c r="G76">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>94</v>
       </c>
-      <c r="B76" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
-        <v>9.99</v>
-      </c>
-      <c r="E76">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>95</v>
-      </c>
-      <c r="B77" t="s">
-        <v>96</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -2374,217 +2840,295 @@
       <c r="E77">
         <v>22</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F77">
+        <v>20</v>
+      </c>
+      <c r="G77">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" t="s">
         <v>97</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>9.99</v>
+      </c>
+      <c r="E78">
+        <v>15</v>
+      </c>
+      <c r="F78">
+        <v>13.5</v>
+      </c>
+      <c r="G78">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>98</v>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>9.99</v>
-      </c>
-      <c r="E78">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>99</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>9.99</v>
+      </c>
+      <c r="E79">
+        <v>15</v>
+      </c>
+      <c r="F79">
+        <v>13.5</v>
+      </c>
+      <c r="G79">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>100</v>
       </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79">
-        <v>9.99</v>
-      </c>
-      <c r="E79">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>101</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>9.99</v>
+      </c>
+      <c r="E80">
+        <v>15</v>
+      </c>
+      <c r="F80">
+        <v>13.5</v>
+      </c>
+      <c r="G80">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
         <v>102</v>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>9.99</v>
-      </c>
-      <c r="E80">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>9.99</v>
+      </c>
+      <c r="E81">
+        <v>15</v>
+      </c>
+      <c r="F81">
+        <v>13.5</v>
+      </c>
+      <c r="G81">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
         <v>103</v>
       </c>
-      <c r="B81" t="s">
-        <v>102</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>9.99</v>
-      </c>
-      <c r="E81">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>104</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>9.99</v>
+      </c>
+      <c r="E82">
+        <v>15</v>
+      </c>
+      <c r="F82">
+        <v>13.5</v>
+      </c>
+      <c r="G82">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>105</v>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>9.99</v>
-      </c>
-      <c r="E82">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>9.99</v>
+      </c>
+      <c r="E83">
+        <v>15</v>
+      </c>
+      <c r="F83">
+        <v>13.5</v>
+      </c>
+      <c r="G83">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>106</v>
       </c>
-      <c r="B83" t="s">
-        <v>105</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>9.99</v>
-      </c>
-      <c r="E83">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>9.99</v>
+      </c>
+      <c r="E84">
+        <v>15</v>
+      </c>
+      <c r="F84">
+        <v>13.5</v>
+      </c>
+      <c r="G84">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>107</v>
       </c>
-      <c r="B84" t="s">
-        <v>105</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>9.99</v>
-      </c>
-      <c r="E84">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>9.99</v>
+      </c>
+      <c r="E85">
+        <v>15</v>
+      </c>
+      <c r="F85">
+        <v>13.5</v>
+      </c>
+      <c r="G85">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>108</v>
       </c>
-      <c r="B85" t="s">
-        <v>105</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>9.99</v>
-      </c>
-      <c r="E85">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>9.99</v>
+      </c>
+      <c r="E86">
+        <v>15</v>
+      </c>
+      <c r="F86">
+        <v>13.5</v>
+      </c>
+      <c r="G86">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
         <v>109</v>
       </c>
-      <c r="B86" t="s">
-        <v>105</v>
-      </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86">
-        <v>9.99</v>
-      </c>
-      <c r="E86">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>9.99</v>
+      </c>
+      <c r="E87">
+        <v>15</v>
+      </c>
+      <c r="F87">
+        <v>13.5</v>
+      </c>
+      <c r="G87">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>110</v>
       </c>
-      <c r="B87" t="s">
-        <v>105</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
-        <v>9.99</v>
-      </c>
-      <c r="E87">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
+        <v>104</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>9.99</v>
+      </c>
+      <c r="E88">
+        <v>15</v>
+      </c>
+      <c r="F88">
+        <v>13.5</v>
+      </c>
+      <c r="G88">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>111</v>
       </c>
-      <c r="B88" t="s">
-        <v>105</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>9.99</v>
-      </c>
-      <c r="E88">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>112</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>9.99</v>
+      </c>
+      <c r="E89">
+        <v>15</v>
+      </c>
+      <c r="F89">
+        <v>13.5</v>
+      </c>
+      <c r="G89">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>113</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>9.99</v>
-      </c>
-      <c r="E89">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>114</v>
-      </c>
-      <c r="B90" t="s">
-        <v>115</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -2595,13 +3139,19 @@
       <c r="E90">
         <v>20</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F90">
+        <v>16</v>
+      </c>
+      <c r="G90">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -2612,13 +3162,19 @@
       <c r="E91">
         <v>22</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F91">
+        <v>20</v>
+      </c>
+      <c r="G91">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B92" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2629,13 +3185,19 @@
       <c r="E92">
         <v>22</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F92">
+        <v>20</v>
+      </c>
+      <c r="G92">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B93" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -2646,13 +3208,19 @@
       <c r="E93">
         <v>22</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F93">
+        <v>20</v>
+      </c>
+      <c r="G93">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -2663,13 +3231,19 @@
       <c r="E94">
         <v>22</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F94">
+        <v>20</v>
+      </c>
+      <c r="G94">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2680,13 +3254,19 @@
       <c r="E95">
         <v>28</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F95">
+        <v>27</v>
+      </c>
+      <c r="G95">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -2697,13 +3277,19 @@
       <c r="E96">
         <v>25</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F96">
+        <v>24</v>
+      </c>
+      <c r="G96">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B97" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -2714,13 +3300,19 @@
       <c r="E97">
         <v>25</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F97">
+        <v>24</v>
+      </c>
+      <c r="G97">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B98" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2731,13 +3323,19 @@
       <c r="E98">
         <v>25</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F98">
+        <v>24</v>
+      </c>
+      <c r="G98">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B99" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -2748,13 +3346,19 @@
       <c r="E99">
         <v>25</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F99">
+        <v>24</v>
+      </c>
+      <c r="G99">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -2765,13 +3369,19 @@
       <c r="E100">
         <v>25</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F100">
+        <v>24</v>
+      </c>
+      <c r="G100">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -2782,13 +3392,19 @@
       <c r="E101">
         <v>28</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F101">
+        <v>27</v>
+      </c>
+      <c r="G101">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B102" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -2799,13 +3415,19 @@
       <c r="E102">
         <v>22</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F102">
+        <v>20</v>
+      </c>
+      <c r="G102">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -2816,13 +3438,19 @@
       <c r="E103">
         <v>28</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F103">
+        <v>27</v>
+      </c>
+      <c r="G103">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -2833,13 +3461,19 @@
       <c r="E104">
         <v>22</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F104">
+        <v>20</v>
+      </c>
+      <c r="G104">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -2850,13 +3484,19 @@
       <c r="E105">
         <v>28</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F105">
+        <v>27</v>
+      </c>
+      <c r="G105">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -2867,13 +3507,19 @@
       <c r="E106">
         <v>28</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F106">
+        <v>27</v>
+      </c>
+      <c r="G106">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -2884,13 +3530,19 @@
       <c r="E107">
         <v>22</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F107">
+        <v>20</v>
+      </c>
+      <c r="G107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -2901,13 +3553,19 @@
       <c r="E108">
         <v>22</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F108">
+        <v>20</v>
+      </c>
+      <c r="G108">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -2918,13 +3576,19 @@
       <c r="E109">
         <v>25</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F109">
+        <v>24</v>
+      </c>
+      <c r="G109">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -2935,13 +3599,19 @@
       <c r="E110">
         <v>20</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F110">
+        <v>16</v>
+      </c>
+      <c r="G110">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -2952,13 +3622,19 @@
       <c r="E111">
         <v>20</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F111">
+        <v>16</v>
+      </c>
+      <c r="G111">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -2969,13 +3645,19 @@
       <c r="E112">
         <v>20</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F112">
+        <v>16</v>
+      </c>
+      <c r="G112">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B113" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -2986,13 +3668,19 @@
       <c r="E113">
         <v>20</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F113">
+        <v>16</v>
+      </c>
+      <c r="G113">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -3003,13 +3691,19 @@
       <c r="E114">
         <v>22</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F114">
+        <v>21.5</v>
+      </c>
+      <c r="G114">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -3020,13 +3714,19 @@
       <c r="E115">
         <v>28</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F115">
+        <v>27</v>
+      </c>
+      <c r="G115">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -3037,13 +3737,19 @@
       <c r="E116">
         <v>22</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F116">
+        <v>20</v>
+      </c>
+      <c r="G116">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -3054,30 +3760,42 @@
       <c r="E117">
         <v>22</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F117">
+        <v>20</v>
+      </c>
+      <c r="G117">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>142</v>
+      </c>
+      <c r="B118" t="s">
         <v>143</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118">
+        <v>9.99</v>
+      </c>
+      <c r="E118">
+        <v>15</v>
+      </c>
+      <c r="F118">
+        <v>13.5</v>
+      </c>
+      <c r="G118">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
         <v>144</v>
       </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
-      <c r="D118">
-        <v>9.99</v>
-      </c>
-      <c r="E118">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+      <c r="B119" t="s">
         <v>145</v>
-      </c>
-      <c r="B119" t="s">
-        <v>146</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -3088,47 +3806,65 @@
       <c r="E119">
         <v>20</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F119">
+        <v>16</v>
+      </c>
+      <c r="G119">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>146</v>
+      </c>
+      <c r="B120" t="s">
         <v>147</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>9.99</v>
+      </c>
+      <c r="E120">
+        <v>15</v>
+      </c>
+      <c r="F120">
+        <v>13.5</v>
+      </c>
+      <c r="G120">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>148</v>
       </c>
-      <c r="C120">
-        <v>1</v>
-      </c>
-      <c r="D120">
-        <v>9.99</v>
-      </c>
-      <c r="E120">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>149</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>9.99</v>
+      </c>
+      <c r="E121">
+        <v>15</v>
+      </c>
+      <c r="F121">
+        <v>13.5</v>
+      </c>
+      <c r="G121">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
         <v>150</v>
       </c>
-      <c r="C121">
-        <v>1</v>
-      </c>
-      <c r="D121">
-        <v>9.99</v>
-      </c>
-      <c r="E121">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>151</v>
-      </c>
       <c r="B122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -3139,13 +3875,19 @@
       <c r="E122">
         <v>20</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F122">
+        <v>16</v>
+      </c>
+      <c r="G122">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B123" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -3156,13 +3898,19 @@
       <c r="E123">
         <v>28</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F123">
+        <v>27</v>
+      </c>
+      <c r="G123">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -3173,13 +3921,19 @@
       <c r="E124">
         <v>22</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F124">
+        <v>21.5</v>
+      </c>
+      <c r="G124">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B125" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -3190,13 +3944,19 @@
       <c r="E125">
         <v>20</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F125">
+        <v>16</v>
+      </c>
+      <c r="G125">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>154</v>
+      </c>
+      <c r="B126" t="s">
         <v>155</v>
-      </c>
-      <c r="B126" t="s">
-        <v>156</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -3207,13 +3967,19 @@
       <c r="E126">
         <v>28</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F126">
+        <v>27</v>
+      </c>
+      <c r="G126">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B127" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -3224,13 +3990,19 @@
       <c r="E127">
         <v>28</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F127">
+        <v>27</v>
+      </c>
+      <c r="G127">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B128" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -3241,13 +4013,19 @@
       <c r="E128">
         <v>28</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F128">
+        <v>27</v>
+      </c>
+      <c r="G128">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B129" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -3258,13 +4036,19 @@
       <c r="E129">
         <v>28</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F129">
+        <v>27</v>
+      </c>
+      <c r="G129">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B130" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -3275,30 +4059,42 @@
       <c r="E130">
         <v>28</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F130">
+        <v>27</v>
+      </c>
+      <c r="G130">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>160</v>
+      </c>
+      <c r="B131" t="s">
         <v>161</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>9.99</v>
+      </c>
+      <c r="E131">
+        <v>15</v>
+      </c>
+      <c r="F131">
+        <v>13.5</v>
+      </c>
+      <c r="G131">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
         <v>162</v>
       </c>
-      <c r="C131">
-        <v>1</v>
-      </c>
-      <c r="D131">
-        <v>9.99</v>
-      </c>
-      <c r="E131">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>163</v>
-      </c>
-      <c r="B132" t="s">
-        <v>164</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -3309,13 +4105,19 @@
       <c r="E132">
         <v>22</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F132">
+        <v>20</v>
+      </c>
+      <c r="G132">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B133" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -3326,13 +4128,19 @@
       <c r="E133">
         <v>22</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F133">
+        <v>20</v>
+      </c>
+      <c r="G133">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B134" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -3343,13 +4151,19 @@
       <c r="E134">
         <v>22</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F134">
+        <v>20</v>
+      </c>
+      <c r="G134">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B135" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -3360,13 +4174,19 @@
       <c r="E135">
         <v>22</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F135">
+        <v>20</v>
+      </c>
+      <c r="G135">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B136" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -3377,132 +4197,180 @@
       <c r="E136">
         <v>22</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F136">
+        <v>20</v>
+      </c>
+      <c r="G136">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>168</v>
+      </c>
+      <c r="B137" t="s">
         <v>169</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>9.99</v>
+      </c>
+      <c r="E137">
+        <v>15</v>
+      </c>
+      <c r="F137">
+        <v>13.5</v>
+      </c>
+      <c r="G137">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
         <v>170</v>
       </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-      <c r="D137">
-        <v>9.99</v>
-      </c>
-      <c r="E137">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
+      <c r="B138" t="s">
         <v>171</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>9.99</v>
+      </c>
+      <c r="E138">
+        <v>15</v>
+      </c>
+      <c r="F138">
+        <v>13.5</v>
+      </c>
+      <c r="G138">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
         <v>172</v>
       </c>
-      <c r="C138">
-        <v>1</v>
-      </c>
-      <c r="D138">
-        <v>9.99</v>
-      </c>
-      <c r="E138">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
+      <c r="B139" t="s">
+        <v>171</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139">
+        <v>9.99</v>
+      </c>
+      <c r="E139">
+        <v>15</v>
+      </c>
+      <c r="F139">
+        <v>13.5</v>
+      </c>
+      <c r="G139">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>173</v>
       </c>
-      <c r="B139" t="s">
-        <v>172</v>
-      </c>
-      <c r="C139">
-        <v>1</v>
-      </c>
-      <c r="D139">
-        <v>9.99</v>
-      </c>
-      <c r="E139">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+      <c r="B140" t="s">
+        <v>171</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>9.99</v>
+      </c>
+      <c r="E140">
+        <v>15</v>
+      </c>
+      <c r="F140">
+        <v>13.5</v>
+      </c>
+      <c r="G140">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
         <v>174</v>
       </c>
-      <c r="B140" t="s">
-        <v>172</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140">
-        <v>9.99</v>
-      </c>
-      <c r="E140">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
+      <c r="B141" t="s">
         <v>175</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>9.99</v>
+      </c>
+      <c r="E141">
+        <v>15</v>
+      </c>
+      <c r="F141">
+        <v>13.5</v>
+      </c>
+      <c r="G141">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
         <v>176</v>
       </c>
-      <c r="C141">
-        <v>1</v>
-      </c>
-      <c r="D141">
-        <v>9.99</v>
-      </c>
-      <c r="E141">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
+      <c r="B142" t="s">
+        <v>175</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>9.99</v>
+      </c>
+      <c r="E142">
+        <v>15</v>
+      </c>
+      <c r="F142">
+        <v>13.5</v>
+      </c>
+      <c r="G142">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
         <v>177</v>
       </c>
-      <c r="B142" t="s">
-        <v>176</v>
-      </c>
-      <c r="C142">
-        <v>1</v>
-      </c>
-      <c r="D142">
-        <v>9.99</v>
-      </c>
-      <c r="E142">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
+      <c r="B143" t="s">
+        <v>175</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>9.99</v>
+      </c>
+      <c r="E143">
+        <v>15</v>
+      </c>
+      <c r="F143">
+        <v>13.5</v>
+      </c>
+      <c r="G143">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
         <v>178</v>
       </c>
-      <c r="B143" t="s">
-        <v>176</v>
-      </c>
-      <c r="C143">
-        <v>1</v>
-      </c>
-      <c r="D143">
-        <v>9.99</v>
-      </c>
-      <c r="E143">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
+      <c r="B144" t="s">
         <v>179</v>
-      </c>
-      <c r="B144" t="s">
-        <v>180</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -3513,268 +4381,364 @@
       <c r="E144">
         <v>20</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F144">
+        <v>16</v>
+      </c>
+      <c r="G144">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
+        <v>180</v>
+      </c>
+      <c r="B145" t="s">
         <v>181</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>9.99</v>
+      </c>
+      <c r="E145">
+        <v>15</v>
+      </c>
+      <c r="F145">
+        <v>13.5</v>
+      </c>
+      <c r="G145">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
         <v>182</v>
       </c>
-      <c r="C145">
-        <v>1</v>
-      </c>
-      <c r="D145">
-        <v>9.99</v>
-      </c>
-      <c r="E145">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
+      <c r="B146" t="s">
+        <v>181</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>9.99</v>
+      </c>
+      <c r="E146">
+        <v>15</v>
+      </c>
+      <c r="F146">
+        <v>13.5</v>
+      </c>
+      <c r="G146">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
         <v>183</v>
       </c>
-      <c r="B146" t="s">
-        <v>182</v>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146">
-        <v>9.99</v>
-      </c>
-      <c r="E146">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
+      <c r="B147" t="s">
+        <v>181</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147">
+        <v>9.99</v>
+      </c>
+      <c r="E147">
+        <v>15</v>
+      </c>
+      <c r="F147">
+        <v>13.5</v>
+      </c>
+      <c r="G147">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
         <v>184</v>
       </c>
-      <c r="B147" t="s">
-        <v>182</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147">
-        <v>9.99</v>
-      </c>
-      <c r="E147">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
+        <v>181</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+      <c r="D148">
+        <v>9.99</v>
+      </c>
+      <c r="E148">
+        <v>15</v>
+      </c>
+      <c r="F148">
+        <v>13.5</v>
+      </c>
+      <c r="G148">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
         <v>185</v>
       </c>
-      <c r="B148" t="s">
-        <v>182</v>
-      </c>
-      <c r="C148">
-        <v>1</v>
-      </c>
-      <c r="D148">
-        <v>9.99</v>
-      </c>
-      <c r="E148">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
+      <c r="B149" t="s">
+        <v>181</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149">
+        <v>9.99</v>
+      </c>
+      <c r="E149">
+        <v>15</v>
+      </c>
+      <c r="F149">
+        <v>13.5</v>
+      </c>
+      <c r="G149">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
         <v>186</v>
       </c>
-      <c r="B149" t="s">
-        <v>182</v>
-      </c>
-      <c r="C149">
-        <v>1</v>
-      </c>
-      <c r="D149">
-        <v>9.99</v>
-      </c>
-      <c r="E149">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
+      <c r="B150" t="s">
+        <v>181</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150">
+        <v>9.99</v>
+      </c>
+      <c r="E150">
+        <v>15</v>
+      </c>
+      <c r="F150">
+        <v>13.5</v>
+      </c>
+      <c r="G150">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
         <v>187</v>
       </c>
-      <c r="B150" t="s">
-        <v>182</v>
-      </c>
-      <c r="C150">
-        <v>1</v>
-      </c>
-      <c r="D150">
-        <v>9.99</v>
-      </c>
-      <c r="E150">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
+      <c r="B151" t="s">
+        <v>181</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>9.99</v>
+      </c>
+      <c r="E151">
+        <v>15</v>
+      </c>
+      <c r="F151">
+        <v>13.5</v>
+      </c>
+      <c r="G151">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
         <v>188</v>
       </c>
-      <c r="B151" t="s">
-        <v>182</v>
-      </c>
-      <c r="C151">
-        <v>1</v>
-      </c>
-      <c r="D151">
-        <v>9.99</v>
-      </c>
-      <c r="E151">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
+      <c r="B152" t="s">
+        <v>181</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>9.99</v>
+      </c>
+      <c r="E152">
+        <v>15</v>
+      </c>
+      <c r="F152">
+        <v>13.5</v>
+      </c>
+      <c r="G152">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
         <v>189</v>
       </c>
-      <c r="B152" t="s">
-        <v>182</v>
-      </c>
-      <c r="C152">
-        <v>1</v>
-      </c>
-      <c r="D152">
-        <v>9.99</v>
-      </c>
-      <c r="E152">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
+      <c r="B153" t="s">
+        <v>181</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>9.99</v>
+      </c>
+      <c r="E153">
+        <v>15</v>
+      </c>
+      <c r="F153">
+        <v>13.5</v>
+      </c>
+      <c r="G153">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
         <v>190</v>
       </c>
-      <c r="B153" t="s">
-        <v>182</v>
-      </c>
-      <c r="C153">
-        <v>1</v>
-      </c>
-      <c r="D153">
-        <v>9.99</v>
-      </c>
-      <c r="E153">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
+      <c r="B154" t="s">
+        <v>181</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>9.99</v>
+      </c>
+      <c r="E154">
+        <v>15</v>
+      </c>
+      <c r="F154">
+        <v>13.5</v>
+      </c>
+      <c r="G154">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
         <v>191</v>
       </c>
-      <c r="B154" t="s">
-        <v>182</v>
-      </c>
-      <c r="C154">
-        <v>1</v>
-      </c>
-      <c r="D154">
-        <v>9.99</v>
-      </c>
-      <c r="E154">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
+      <c r="B155" t="s">
+        <v>181</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155">
+        <v>9.99</v>
+      </c>
+      <c r="E155">
+        <v>15</v>
+      </c>
+      <c r="F155">
+        <v>13.5</v>
+      </c>
+      <c r="G155">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
         <v>192</v>
       </c>
-      <c r="B155" t="s">
-        <v>182</v>
-      </c>
-      <c r="C155">
-        <v>1</v>
-      </c>
-      <c r="D155">
-        <v>9.99</v>
-      </c>
-      <c r="E155">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
+        <v>181</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
+        <v>9.99</v>
+      </c>
+      <c r="E156">
+        <v>15</v>
+      </c>
+      <c r="F156">
+        <v>13.5</v>
+      </c>
+      <c r="G156">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>193</v>
       </c>
-      <c r="B156" t="s">
-        <v>182</v>
-      </c>
-      <c r="C156">
-        <v>1</v>
-      </c>
-      <c r="D156">
-        <v>9.99</v>
-      </c>
-      <c r="E156">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
+      <c r="B157" t="s">
         <v>194</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157">
+        <v>1</v>
+      </c>
+      <c r="D157">
+        <v>9.99</v>
+      </c>
+      <c r="E157">
+        <v>15</v>
+      </c>
+      <c r="F157">
+        <v>13.5</v>
+      </c>
+      <c r="G157">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
         <v>195</v>
       </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-      <c r="D157">
-        <v>9.99</v>
-      </c>
-      <c r="E157">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
+      <c r="B158" t="s">
+        <v>194</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158">
+        <v>9.99</v>
+      </c>
+      <c r="E158">
+        <v>15</v>
+      </c>
+      <c r="F158">
+        <v>13.5</v>
+      </c>
+      <c r="G158">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>196</v>
       </c>
-      <c r="B158" t="s">
-        <v>195</v>
-      </c>
-      <c r="C158">
-        <v>1</v>
-      </c>
-      <c r="D158">
-        <v>9.99</v>
-      </c>
-      <c r="E158">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>197</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159">
+        <v>9.99</v>
+      </c>
+      <c r="E159">
+        <v>15</v>
+      </c>
+      <c r="F159">
+        <v>13.5</v>
+      </c>
+      <c r="G159">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
         <v>198</v>
       </c>
-      <c r="C159">
-        <v>1</v>
-      </c>
-      <c r="D159">
-        <v>9.99</v>
-      </c>
-      <c r="E159">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>199</v>
-      </c>
-      <c r="B160" t="s">
-        <v>200</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -3785,47 +4749,65 @@
       <c r="E160">
         <v>20</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F160">
+        <v>16</v>
+      </c>
+      <c r="G160">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>200</v>
+      </c>
+      <c r="B161" t="s">
         <v>201</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>9.99</v>
+      </c>
+      <c r="E161">
+        <v>15</v>
+      </c>
+      <c r="F161">
+        <v>13.5</v>
+      </c>
+      <c r="G161">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
         <v>202</v>
       </c>
-      <c r="C161">
-        <v>1</v>
-      </c>
-      <c r="D161">
-        <v>9.99</v>
-      </c>
-      <c r="E161">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
+      <c r="B162" t="s">
+        <v>201</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>9.99</v>
+      </c>
+      <c r="E162">
+        <v>15</v>
+      </c>
+      <c r="F162">
+        <v>13.5</v>
+      </c>
+      <c r="G162">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>203</v>
       </c>
-      <c r="B162" t="s">
-        <v>202</v>
-      </c>
-      <c r="C162">
-        <v>1</v>
-      </c>
-      <c r="D162">
-        <v>9.99</v>
-      </c>
-      <c r="E162">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
+      <c r="B163" t="s">
         <v>204</v>
-      </c>
-      <c r="B163" t="s">
-        <v>205</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -3836,11 +4818,19 @@
       <c r="E163">
         <v>30</v>
       </c>
+      <c r="F163">
+        <v>27</v>
+      </c>
+      <c r="G163">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{3D7B2B37-5CE6-B94A-A5ED-A1F69E90AE0D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
